--- a/backtest/results_qmt/七星QMT_交易记录_2026.xlsx
+++ b/backtest/results_qmt/七星QMT_交易记录_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G244"/>
+  <dimension ref="A1:G246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,11 +477,7 @@
       <c r="E2" t="n">
         <v>0.713</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -512,11 +508,7 @@
       <c r="E3" t="n">
         <v>0.73</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -547,11 +539,7 @@
       <c r="E4" t="n">
         <v>0.876</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -582,11 +570,7 @@
       <c r="E5" t="n">
         <v>0.871</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>盈利保护</t>
@@ -617,11 +601,7 @@
       <c r="E6" t="n">
         <v>0.876</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -652,11 +632,7 @@
       <c r="E7" t="n">
         <v>0.9419999999999999</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>盈利保护</t>
@@ -687,11 +663,7 @@
       <c r="E8" t="n">
         <v>0.793</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -722,11 +694,7 @@
       <c r="E9" t="n">
         <v>0.795</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -757,11 +725,7 @@
       <c r="E10" t="n">
         <v>0.9360000000000001</v>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -792,11 +756,7 @@
       <c r="E11" t="n">
         <v>0.906</v>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>盈利保护</t>
@@ -827,11 +787,7 @@
       <c r="E12" t="n">
         <v>1.476</v>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -862,11 +818,7 @@
       <c r="E13" t="n">
         <v>1.537</v>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -897,11 +849,7 @@
       <c r="E14" t="n">
         <v>0.9399999999999999</v>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -932,11 +880,7 @@
       <c r="E15" t="n">
         <v>0.9409999999999999</v>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -967,11 +911,7 @@
       <c r="E16" t="n">
         <v>1.541</v>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -1002,11 +942,7 @@
       <c r="E17" t="n">
         <v>1.509</v>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -1037,11 +973,7 @@
       <c r="E18" t="n">
         <v>1.509</v>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -1072,11 +1004,7 @@
       <c r="E19" t="n">
         <v>1.483</v>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -1107,11 +1035,7 @@
       <c r="E20" t="n">
         <v>1.795</v>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -1142,11 +1066,7 @@
       <c r="E21" t="n">
         <v>1.762</v>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -1177,11 +1097,7 @@
       <c r="E22" t="n">
         <v>1.492</v>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -1212,11 +1128,7 @@
       <c r="E23" t="n">
         <v>1.456</v>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -1247,11 +1159,7 @@
       <c r="E24" t="n">
         <v>1.456</v>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -1282,11 +1190,7 @@
       <c r="E25" t="n">
         <v>1.421</v>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -1317,11 +1221,7 @@
       <c r="E26" t="n">
         <v>1.421</v>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -1352,11 +1252,7 @@
       <c r="E27" t="n">
         <v>1.279</v>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
           <t>盈利保护</t>
@@ -1387,11 +1283,7 @@
       <c r="E28" t="n">
         <v>1.298</v>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -1422,11 +1314,7 @@
       <c r="E29" t="n">
         <v>1.264</v>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -1457,11 +1345,7 @@
       <c r="E30" t="n">
         <v>0.6889999999999999</v>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -1492,11 +1376,7 @@
       <c r="E31" t="n">
         <v>0.676</v>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -1527,11 +1407,7 @@
       <c r="E32" t="n">
         <v>0.676</v>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -1562,11 +1438,7 @@
       <c r="E33" t="n">
         <v>0.6840000000000001</v>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -1597,11 +1469,7 @@
       <c r="E34" t="n">
         <v>0.6840000000000001</v>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -1632,11 +1500,7 @@
       <c r="E35" t="n">
         <v>0.6840000000000001</v>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -1667,11 +1531,7 @@
       <c r="E36" t="n">
         <v>0.8139999999999999</v>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -1702,11 +1562,7 @@
       <c r="E37" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -1737,11 +1593,7 @@
       <c r="E38" t="n">
         <v>0.831</v>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -1772,11 +1624,7 @@
       <c r="E39" t="n">
         <v>0.863</v>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -1807,11 +1655,7 @@
       <c r="E40" t="n">
         <v>1.848</v>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -1842,11 +1686,7 @@
       <c r="E41" t="n">
         <v>1.844</v>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -1877,11 +1717,7 @@
       <c r="E42" t="n">
         <v>1.209</v>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -1912,11 +1748,7 @@
       <c r="E43" t="n">
         <v>1.204</v>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -1947,11 +1779,7 @@
       <c r="E44" t="n">
         <v>1.868</v>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -1982,11 +1810,7 @@
       <c r="E45" t="n">
         <v>1.854</v>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -2017,11 +1841,7 @@
       <c r="E46" t="n">
         <v>1.237</v>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -2052,11 +1872,7 @@
       <c r="E47" t="n">
         <v>1.21</v>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -2087,11 +1903,7 @@
       <c r="E48" t="n">
         <v>1.402</v>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -2122,11 +1934,7 @@
       <c r="E49" t="n">
         <v>1.4</v>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -2157,11 +1965,7 @@
       <c r="E50" t="n">
         <v>1.217</v>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -2192,11 +1996,7 @@
       <c r="E51" t="n">
         <v>1.198</v>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -2227,11 +2027,7 @@
       <c r="E52" t="n">
         <v>1.888</v>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -2262,11 +2058,7 @@
       <c r="E53" t="n">
         <v>1.873</v>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -2297,11 +2089,7 @@
       <c r="E54" t="n">
         <v>0.829</v>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -2332,11 +2120,7 @@
       <c r="E55" t="n">
         <v>0.833</v>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -2367,11 +2151,7 @@
       <c r="E56" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -2402,11 +2182,7 @@
       <c r="E57" t="n">
         <v>0.705</v>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -2437,11 +2213,7 @@
       <c r="E58" t="n">
         <v>1.396</v>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -2472,11 +2244,7 @@
       <c r="E59" t="n">
         <v>1.413</v>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -2507,11 +2275,7 @@
       <c r="E60" t="n">
         <v>0.874</v>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -2542,11 +2306,7 @@
       <c r="E61" t="n">
         <v>0.876</v>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -2577,11 +2337,7 @@
       <c r="E62" t="n">
         <v>1.176</v>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -2612,11 +2368,7 @@
       <c r="E63" t="n">
         <v>1.169</v>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -2647,11 +2399,7 @@
       <c r="E64" t="n">
         <v>0.855</v>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -2682,11 +2430,7 @@
       <c r="E65" t="n">
         <v>0.865</v>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -2717,11 +2461,7 @@
       <c r="E66" t="n">
         <v>1.179</v>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -2752,11 +2492,7 @@
       <c r="E67" t="n">
         <v>1.216</v>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -2787,11 +2523,7 @@
       <c r="E68" t="n">
         <v>1.574</v>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -2822,11 +2554,7 @@
       <c r="E69" t="n">
         <v>1.723</v>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
           <t>盈利保护</t>
@@ -2857,11 +2585,7 @@
       <c r="E70" t="n">
         <v>0.923</v>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -2892,11 +2616,7 @@
       <c r="E71" t="n">
         <v>0.93</v>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -2927,11 +2647,7 @@
       <c r="E72" t="n">
         <v>1.734</v>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -2962,11 +2678,7 @@
       <c r="E73" t="n">
         <v>2.548</v>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
           <t>盈利保护</t>
@@ -2997,11 +2709,7 @@
       <c r="E74" t="n">
         <v>3.128</v>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -3032,11 +2740,7 @@
       <c r="E75" t="n">
         <v>3.087</v>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -3067,11 +2771,7 @@
       <c r="E76" t="n">
         <v>3.087</v>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -3102,11 +2802,7 @@
       <c r="E77" t="n">
         <v>3.034</v>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -3137,11 +2833,7 @@
       <c r="E78" t="n">
         <v>1.334</v>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -3172,11 +2864,7 @@
       <c r="E79" t="n">
         <v>1.353</v>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -3207,11 +2895,7 @@
       <c r="E80" t="n">
         <v>1.353</v>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -3242,11 +2926,7 @@
       <c r="E81" t="n">
         <v>1.35</v>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -3277,11 +2957,7 @@
       <c r="E82" t="n">
         <v>1.572</v>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -3312,11 +2988,7 @@
       <c r="E83" t="n">
         <v>1.586</v>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -3347,11 +3019,7 @@
       <c r="E84" t="n">
         <v>1.586</v>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -3382,11 +3050,7 @@
       <c r="E85" t="n">
         <v>1.612</v>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -3417,11 +3081,7 @@
       <c r="E86" t="n">
         <v>2.452</v>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -3452,11 +3112,7 @@
       <c r="E87" t="n">
         <v>2.716</v>
       </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -3487,11 +3143,7 @@
       <c r="E88" t="n">
         <v>1.72</v>
       </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -3522,11 +3174,7 @@
       <c r="E89" t="n">
         <v>1.636</v>
       </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -3557,11 +3205,7 @@
       <c r="E90" t="n">
         <v>0.8120000000000001</v>
       </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -3592,11 +3236,7 @@
       <c r="E91" t="n">
         <v>0.796</v>
       </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -3627,11 +3267,7 @@
       <c r="E92" t="n">
         <v>1.416</v>
       </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -3662,11 +3298,7 @@
       <c r="E93" t="n">
         <v>1.37</v>
       </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -3697,11 +3329,7 @@
       <c r="E94" t="n">
         <v>1.783</v>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -3732,11 +3360,7 @@
       <c r="E95" t="n">
         <v>1.834</v>
       </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -3767,11 +3391,7 @@
       <c r="E96" t="n">
         <v>3.21</v>
       </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -3802,11 +3422,7 @@
       <c r="E97" t="n">
         <v>3.193</v>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -3837,11 +3453,7 @@
       <c r="E98" t="n">
         <v>1.827</v>
       </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -3872,11 +3484,7 @@
       <c r="E99" t="n">
         <v>1.806</v>
       </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -3907,11 +3515,7 @@
       <c r="E100" t="n">
         <v>3.16</v>
       </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -3942,11 +3546,7 @@
       <c r="E101" t="n">
         <v>3.161</v>
       </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -3977,11 +3577,7 @@
       <c r="E102" t="n">
         <v>1.489</v>
       </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -4012,11 +3608,7 @@
       <c r="E103" t="n">
         <v>1.423</v>
       </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
           <t>盈利保护</t>
@@ -4047,11 +3639,7 @@
       <c r="E104" t="n">
         <v>1.217</v>
       </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -4082,11 +3670,7 @@
       <c r="E105" t="n">
         <v>1.243</v>
       </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -4117,11 +3701,7 @@
       <c r="E106" t="n">
         <v>1.19</v>
       </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -4152,11 +3732,7 @@
       <c r="E107" t="n">
         <v>1.184</v>
       </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -4187,11 +3763,7 @@
       <c r="E108" t="n">
         <v>1.493</v>
       </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -4222,11 +3794,7 @@
       <c r="E109" t="n">
         <v>1.475</v>
       </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -4257,11 +3825,7 @@
       <c r="E110" t="n">
         <v>1.275</v>
       </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -4292,11 +3856,7 @@
       <c r="E111" t="n">
         <v>1.26</v>
       </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -4327,11 +3887,7 @@
       <c r="E112" t="n">
         <v>1.502</v>
       </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -4362,11 +3918,7 @@
       <c r="E113" t="n">
         <v>1.48</v>
       </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -4397,11 +3949,7 @@
       <c r="E114" t="n">
         <v>1.217</v>
       </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -4432,11 +3980,7 @@
       <c r="E115" t="n">
         <v>1.228</v>
       </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -4467,11 +4011,7 @@
       <c r="E116" t="n">
         <v>1.228</v>
       </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -4502,11 +4042,7 @@
       <c r="E117" t="n">
         <v>1.202</v>
       </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -4537,11 +4073,7 @@
       <c r="E118" t="n">
         <v>1.509</v>
       </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -4572,11 +4104,7 @@
       <c r="E119" t="n">
         <v>1.563</v>
       </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -4607,11 +4135,7 @@
       <c r="E120" t="n">
         <v>1.244</v>
       </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -4642,11 +4166,7 @@
       <c r="E121" t="n">
         <v>1.251</v>
       </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -4677,11 +4197,7 @@
       <c r="E122" t="n">
         <v>1.595</v>
       </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -4712,11 +4228,7 @@
       <c r="E123" t="n">
         <v>1.601</v>
       </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -4747,11 +4259,7 @@
       <c r="E124" t="n">
         <v>2.941</v>
       </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -4782,11 +4290,7 @@
       <c r="E125" t="n">
         <v>3.032</v>
       </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -4817,11 +4321,7 @@
       <c r="E126" t="n">
         <v>1.602</v>
       </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -4852,11 +4352,7 @@
       <c r="E127" t="n">
         <v>1.58</v>
       </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -4887,11 +4383,7 @@
       <c r="E128" t="n">
         <v>3.059</v>
       </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -4922,11 +4414,7 @@
       <c r="E129" t="n">
         <v>2.939</v>
       </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -4957,11 +4445,7 @@
       <c r="E130" t="n">
         <v>1.593</v>
       </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -4992,11 +4476,7 @@
       <c r="E131" t="n">
         <v>1.582</v>
       </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -5027,11 +4507,7 @@
       <c r="E132" t="n">
         <v>2.976</v>
       </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -5062,11 +4538,7 @@
       <c r="E133" t="n">
         <v>3.143</v>
       </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -5097,11 +4569,7 @@
       <c r="E134" t="n">
         <v>1.407</v>
       </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -5132,11 +4600,7 @@
       <c r="E135" t="n">
         <v>1.453</v>
       </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -5167,11 +4631,7 @@
       <c r="E136" t="n">
         <v>1.609</v>
       </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -5202,11 +4662,7 @@
       <c r="E137" t="n">
         <v>1.82</v>
       </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
           <t>盈利保护</t>
@@ -5237,11 +4693,7 @@
       <c r="E138" t="n">
         <v>2.748</v>
       </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -5272,11 +4724,7 @@
       <c r="E139" t="n">
         <v>2.998</v>
       </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -5307,11 +4755,7 @@
       <c r="E140" t="n">
         <v>2.998</v>
       </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -5342,11 +4786,7 @@
       <c r="E141" t="n">
         <v>3.071</v>
       </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -5377,11 +4817,7 @@
       <c r="E142" t="n">
         <v>3.071</v>
       </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -5412,11 +4848,7 @@
       <c r="E143" t="n">
         <v>3.094</v>
       </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -5447,11 +4879,7 @@
       <c r="E144" t="n">
         <v>1.495</v>
       </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -5482,11 +4910,7 @@
       <c r="E145" t="n">
         <v>1.526</v>
       </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -5517,11 +4941,7 @@
       <c r="E146" t="n">
         <v>1.705</v>
       </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -5552,11 +4972,7 @@
       <c r="E147" t="n">
         <v>1.625</v>
       </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr">
         <is>
           <t>盈利保护</t>
@@ -5587,11 +5003,7 @@
       <c r="E148" t="n">
         <v>2.184</v>
       </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -5622,11 +5034,7 @@
       <c r="E149" t="n">
         <v>2.253</v>
       </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -5657,11 +5065,7 @@
       <c r="E150" t="n">
         <v>2.253</v>
       </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -5692,11 +5096,7 @@
       <c r="E151" t="n">
         <v>2.236</v>
       </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -5727,11 +5127,7 @@
       <c r="E152" t="n">
         <v>1.672</v>
       </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -5762,11 +5158,7 @@
       <c r="E153" t="n">
         <v>1.689</v>
       </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr">
         <is>
           <t>盈利保护</t>
@@ -5797,11 +5189,7 @@
       <c r="E154" t="n">
         <v>2.414</v>
       </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F154" t="inlineStr"/>
       <c r="G154" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -5832,11 +5220,7 @@
       <c r="E155" t="n">
         <v>2.391</v>
       </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F155" t="inlineStr"/>
       <c r="G155" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -5867,11 +5251,7 @@
       <c r="E156" t="n">
         <v>2.391</v>
       </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -5902,11 +5282,7 @@
       <c r="E157" t="n">
         <v>2.339</v>
       </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F157" t="inlineStr"/>
       <c r="G157" t="inlineStr">
         <is>
           <t>盈利保护</t>
@@ -5937,11 +5313,7 @@
       <c r="E158" t="n">
         <v>1.327</v>
       </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F158" t="inlineStr"/>
       <c r="G158" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -5972,11 +5344,7 @@
       <c r="E159" t="n">
         <v>1.258</v>
       </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F159" t="inlineStr"/>
       <c r="G159" t="inlineStr">
         <is>
           <t>盈利保护</t>
@@ -6007,11 +5375,7 @@
       <c r="E160" t="n">
         <v>1.593</v>
       </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F160" t="inlineStr"/>
       <c r="G160" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -6042,11 +5406,7 @@
       <c r="E161" t="n">
         <v>1.66</v>
       </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F161" t="inlineStr"/>
       <c r="G161" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -6077,11 +5437,7 @@
       <c r="E162" t="n">
         <v>2.249</v>
       </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -6112,11 +5468,7 @@
       <c r="E163" t="n">
         <v>2.144</v>
       </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr">
         <is>
           <t>盈利保护</t>
@@ -6147,11 +5499,7 @@
       <c r="E164" t="n">
         <v>10.523</v>
       </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F164" t="inlineStr"/>
       <c r="G164" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -6182,11 +5530,7 @@
       <c r="E165" t="n">
         <v>10.719</v>
       </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F165" t="inlineStr"/>
       <c r="G165" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -6217,11 +5561,7 @@
       <c r="E166" t="n">
         <v>1.144</v>
       </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F166" t="inlineStr"/>
       <c r="G166" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -6252,11 +5592,7 @@
       <c r="E167" t="n">
         <v>1.114</v>
       </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F167" t="inlineStr"/>
       <c r="G167" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -6287,11 +5623,7 @@
       <c r="E168" t="n">
         <v>1.185</v>
       </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -6322,11 +5654,7 @@
       <c r="E169" t="n">
         <v>1.176</v>
       </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F169" t="inlineStr"/>
       <c r="G169" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -6357,11 +5685,7 @@
       <c r="E170" t="n">
         <v>2.082</v>
       </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F170" t="inlineStr"/>
       <c r="G170" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -6392,11 +5716,7 @@
       <c r="E171" t="n">
         <v>1.998</v>
       </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F171" t="inlineStr"/>
       <c r="G171" t="inlineStr">
         <is>
           <t>盈利保护</t>
@@ -6427,11 +5747,7 @@
       <c r="E172" t="n">
         <v>1.191</v>
       </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F172" t="inlineStr"/>
       <c r="G172" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -6462,11 +5778,7 @@
       <c r="E173" t="n">
         <v>1.167</v>
       </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F173" t="inlineStr"/>
       <c r="G173" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -6497,11 +5809,7 @@
       <c r="E174" t="n">
         <v>1.372</v>
       </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F174" t="inlineStr"/>
       <c r="G174" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -6532,11 +5840,7 @@
       <c r="E175" t="n">
         <v>1.386</v>
       </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F175" t="inlineStr"/>
       <c r="G175" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -6567,11 +5871,7 @@
       <c r="E176" t="n">
         <v>1.86</v>
       </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F176" t="inlineStr"/>
       <c r="G176" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -6602,11 +5902,7 @@
       <c r="E177" t="n">
         <v>1.859</v>
       </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F177" t="inlineStr"/>
       <c r="G177" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -6637,11 +5933,7 @@
       <c r="E178" t="n">
         <v>1.391</v>
       </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F178" t="inlineStr"/>
       <c r="G178" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -6672,11 +5964,7 @@
       <c r="E179" t="n">
         <v>1.391</v>
       </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F179" t="inlineStr"/>
       <c r="G179" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -6707,11 +5995,7 @@
       <c r="E180" t="n">
         <v>2.232</v>
       </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F180" t="inlineStr"/>
       <c r="G180" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -6742,11 +6026,7 @@
       <c r="E181" t="n">
         <v>2.179</v>
       </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr">
         <is>
           <t>盈利保护</t>
@@ -6777,11 +6057,7 @@
       <c r="E182" t="n">
         <v>1.389</v>
       </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F182" t="inlineStr"/>
       <c r="G182" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -6812,11 +6088,7 @@
       <c r="E183" t="n">
         <v>1.401</v>
       </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F183" t="inlineStr"/>
       <c r="G183" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -6847,11 +6119,7 @@
       <c r="E184" t="n">
         <v>2.244</v>
       </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F184" t="inlineStr"/>
       <c r="G184" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -6882,11 +6150,7 @@
       <c r="E185" t="n">
         <v>2.321</v>
       </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F185" t="inlineStr"/>
       <c r="G185" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -6917,11 +6181,7 @@
       <c r="E186" t="n">
         <v>1.639</v>
       </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F186" t="inlineStr"/>
       <c r="G186" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -6952,11 +6212,7 @@
       <c r="E187" t="n">
         <v>1.647</v>
       </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F187" t="inlineStr"/>
       <c r="G187" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -6987,11 +6243,7 @@
       <c r="E188" t="n">
         <v>2.07</v>
       </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F188" t="inlineStr"/>
       <c r="G188" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -7022,11 +6274,7 @@
       <c r="E189" t="n">
         <v>2.012</v>
       </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F189" t="inlineStr"/>
       <c r="G189" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -7057,11 +6305,7 @@
       <c r="E190" t="n">
         <v>1.634</v>
       </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F190" t="inlineStr"/>
       <c r="G190" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -7092,11 +6336,7 @@
       <c r="E191" t="n">
         <v>1.72</v>
       </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -7127,11 +6367,7 @@
       <c r="E192" t="n">
         <v>2.242</v>
       </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F192" t="inlineStr"/>
       <c r="G192" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -7162,11 +6398,7 @@
       <c r="E193" t="n">
         <v>2.159</v>
       </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F193" t="inlineStr"/>
       <c r="G193" t="inlineStr">
         <is>
           <t>盈利保护</t>
@@ -7197,11 +6429,7 @@
       <c r="E194" t="n">
         <v>1.188</v>
       </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -7232,11 +6460,7 @@
       <c r="E195" t="n">
         <v>1.185</v>
       </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -7267,11 +6491,7 @@
       <c r="E196" t="n">
         <v>1.71</v>
       </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F196" t="inlineStr"/>
       <c r="G196" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -7302,11 +6522,7 @@
       <c r="E197" t="n">
         <v>1.72</v>
       </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr">
         <is>
           <t>盈利保护</t>
@@ -7337,11 +6553,7 @@
       <c r="E198" t="n">
         <v>1.198</v>
       </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -7372,11 +6584,7 @@
       <c r="E199" t="n">
         <v>1.201</v>
       </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F199" t="inlineStr"/>
       <c r="G199" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -7407,11 +6615,7 @@
       <c r="E200" t="n">
         <v>1.699</v>
       </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F200" t="inlineStr"/>
       <c r="G200" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -7442,11 +6646,7 @@
       <c r="E201" t="n">
         <v>1.64</v>
       </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F201" t="inlineStr"/>
       <c r="G201" t="inlineStr">
         <is>
           <t>盈利保护</t>
@@ -7477,11 +6677,7 @@
       <c r="E202" t="n">
         <v>1.19</v>
       </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F202" t="inlineStr"/>
       <c r="G202" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -7512,11 +6708,7 @@
       <c r="E203" t="n">
         <v>1.183</v>
       </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F203" t="inlineStr"/>
       <c r="G203" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -7547,11 +6739,7 @@
       <c r="E204" t="n">
         <v>1.663</v>
       </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F204" t="inlineStr"/>
       <c r="G204" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -7582,11 +6770,7 @@
       <c r="E205" t="n">
         <v>1.615</v>
       </c>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F205" t="inlineStr"/>
       <c r="G205" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -7617,11 +6801,7 @@
       <c r="E206" t="n">
         <v>1.237</v>
       </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F206" t="inlineStr"/>
       <c r="G206" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -7652,11 +6832,7 @@
       <c r="E207" t="n">
         <v>1.231</v>
       </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F207" t="inlineStr"/>
       <c r="G207" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -7687,11 +6863,7 @@
       <c r="E208" t="n">
         <v>1.786</v>
       </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F208" t="inlineStr"/>
       <c r="G208" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -7722,11 +6894,7 @@
       <c r="E209" t="n">
         <v>1.799</v>
       </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F209" t="inlineStr"/>
       <c r="G209" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -7757,11 +6925,7 @@
       <c r="E210" t="n">
         <v>2.136</v>
       </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F210" t="inlineStr"/>
       <c r="G210" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -7792,11 +6956,7 @@
       <c r="E211" t="n">
         <v>2.104</v>
       </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F211" t="inlineStr"/>
       <c r="G211" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -7827,11 +6987,7 @@
       <c r="E212" t="n">
         <v>1.494</v>
       </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F212" t="inlineStr"/>
       <c r="G212" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -7862,11 +7018,7 @@
       <c r="E213" t="n">
         <v>1.505</v>
       </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F213" t="inlineStr"/>
       <c r="G213" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -7897,11 +7049,7 @@
       <c r="E214" t="n">
         <v>2.179</v>
       </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F214" t="inlineStr"/>
       <c r="G214" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -7932,11 +7080,7 @@
       <c r="E215" t="n">
         <v>2.118</v>
       </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F215" t="inlineStr"/>
       <c r="G215" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -7967,11 +7111,7 @@
       <c r="E216" t="n">
         <v>2.118</v>
       </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F216" t="inlineStr"/>
       <c r="G216" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -8002,11 +7142,7 @@
       <c r="E217" t="n">
         <v>2.095</v>
       </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F217" t="inlineStr"/>
       <c r="G217" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -8037,11 +7173,7 @@
       <c r="E218" t="n">
         <v>1.51</v>
       </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F218" t="inlineStr"/>
       <c r="G218" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -8072,11 +7204,7 @@
       <c r="E219" t="n">
         <v>1.458</v>
       </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F219" t="inlineStr"/>
       <c r="G219" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -8107,11 +7235,7 @@
       <c r="E220" t="n">
         <v>2.043</v>
       </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F220" t="inlineStr"/>
       <c r="G220" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -8142,11 +7266,7 @@
       <c r="E221" t="n">
         <v>2.14</v>
       </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F221" t="inlineStr"/>
       <c r="G221" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -8177,11 +7297,7 @@
       <c r="E222" t="n">
         <v>1.377</v>
       </c>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F222" t="inlineStr"/>
       <c r="G222" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -8212,11 +7328,7 @@
       <c r="E223" t="n">
         <v>1.399</v>
       </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F223" t="inlineStr"/>
       <c r="G223" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -8247,11 +7359,7 @@
       <c r="E224" t="n">
         <v>1.518</v>
       </c>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F224" t="inlineStr"/>
       <c r="G224" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -8282,11 +7390,7 @@
       <c r="E225" t="n">
         <v>1.571</v>
       </c>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F225" t="inlineStr"/>
       <c r="G225" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -8317,11 +7421,7 @@
       <c r="E226" t="n">
         <v>2.107</v>
       </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F226" t="inlineStr"/>
       <c r="G226" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -8352,11 +7452,7 @@
       <c r="E227" t="n">
         <v>2.147</v>
       </c>
-      <c r="F227" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F227" t="inlineStr"/>
       <c r="G227" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -8387,11 +7483,7 @@
       <c r="E228" t="n">
         <v>2.108</v>
       </c>
-      <c r="F228" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F228" t="inlineStr"/>
       <c r="G228" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -8422,11 +7514,7 @@
       <c r="E229" t="n">
         <v>2.081</v>
       </c>
-      <c r="F229" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F229" t="inlineStr"/>
       <c r="G229" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -8457,11 +7545,7 @@
       <c r="E230" t="n">
         <v>1.623</v>
       </c>
-      <c r="F230" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F230" t="inlineStr"/>
       <c r="G230" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -8492,11 +7576,7 @@
       <c r="E231" t="n">
         <v>1.636</v>
       </c>
-      <c r="F231" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F231" t="inlineStr"/>
       <c r="G231" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -8527,11 +7607,7 @@
       <c r="E232" t="n">
         <v>4.054</v>
       </c>
-      <c r="F232" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F232" t="inlineStr"/>
       <c r="G232" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -8562,11 +7638,7 @@
       <c r="E233" t="n">
         <v>3.959</v>
       </c>
-      <c r="F233" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F233" t="inlineStr"/>
       <c r="G233" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -8597,11 +7669,7 @@
       <c r="E234" t="n">
         <v>1.762</v>
       </c>
-      <c r="F234" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F234" t="inlineStr"/>
       <c r="G234" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -8632,11 +7700,7 @@
       <c r="E235" t="n">
         <v>1.733</v>
       </c>
-      <c r="F235" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F235" t="inlineStr"/>
       <c r="G235" t="inlineStr">
         <is>
           <t>盈利保护</t>
@@ -8667,11 +7731,7 @@
       <c r="E236" t="n">
         <v>1.517</v>
       </c>
-      <c r="F236" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F236" t="inlineStr"/>
       <c r="G236" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -8702,11 +7762,7 @@
       <c r="E237" t="n">
         <v>1.511</v>
       </c>
-      <c r="F237" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F237" t="inlineStr"/>
       <c r="G237" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -8737,11 +7793,7 @@
       <c r="E238" t="n">
         <v>2.43</v>
       </c>
-      <c r="F238" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F238" t="inlineStr"/>
       <c r="G238" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -8772,11 +7824,7 @@
       <c r="E239" t="n">
         <v>2.477</v>
       </c>
-      <c r="F239" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F239" t="inlineStr"/>
       <c r="G239" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -8807,11 +7855,7 @@
       <c r="E240" t="n">
         <v>1.529</v>
       </c>
-      <c r="F240" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F240" t="inlineStr"/>
       <c r="G240" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -8842,11 +7886,7 @@
       <c r="E241" t="n">
         <v>1.548</v>
       </c>
-      <c r="F241" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F241" t="inlineStr"/>
       <c r="G241" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -8877,11 +7917,7 @@
       <c r="E242" t="n">
         <v>2.536</v>
       </c>
-      <c r="F242" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F242" t="inlineStr"/>
       <c r="G242" t="inlineStr">
         <is>
           <t>排名1</t>
@@ -8912,11 +7948,7 @@
       <c r="E243" t="n">
         <v>2.631</v>
       </c>
-      <c r="F243" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F243" t="inlineStr"/>
       <c r="G243" t="inlineStr">
         <is>
           <t>调出目标</t>
@@ -8947,14 +7979,76 @@
       <c r="E244" t="n">
         <v>1.857</v>
       </c>
-      <c r="F244" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="F244" t="inlineStr"/>
       <c r="G244" t="inlineStr">
         <is>
           <t>排名1</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:59</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>科创50ETF易方达</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>sh588080</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E245" t="n">
+        <v>1.793</v>
+      </c>
+      <c r="F245" t="n">
+        <v>1.2375</v>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>短期动量负(-0.34)</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:59</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>中韩半导体ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>sh513310</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E246" t="n">
+        <v>6.118</v>
+      </c>
+      <c r="F246" t="n">
+        <v>16.1711</v>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>动量排名第1/51</t>
         </is>
       </c>
     </row>

--- a/backtest/results_qmt/七星QMT_交易记录_2026.xlsx
+++ b/backtest/results_qmt/七星QMT_交易记录_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G246"/>
+  <dimension ref="A1:G262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8052,6 +8052,534 @@
         </is>
       </c>
     </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-06-05 14:49</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>中韩半导体ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>sh513310</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E247" t="n">
+        <v>5.613</v>
+      </c>
+      <c r="F247" t="n">
+        <v>10.9997</v>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>盈利保护(回撤7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-06-05 14:49</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>创业板成长ETF华夏</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>sz159967</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E248" t="n">
+        <v>0.921</v>
+      </c>
+      <c r="F248" t="n">
+        <v>4.3759</v>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>动量排名第1/51</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-06-08 13:21</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>创业板成长ETF华夏</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>sz159967</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E249" t="n">
+        <v>0.888</v>
+      </c>
+      <c r="F249" t="n">
+        <v>3.5728</v>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>盈利保护(回撤6%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-06-08 13:21</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>日经ETF华夏</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>sh513520</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E250" t="n">
+        <v>2.227</v>
+      </c>
+      <c r="F250" t="n">
+        <v>1.1717</v>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>动量排名第1/51</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-06-09 10:58</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>日经ETF华夏</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>sh513520</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E251" t="n">
+        <v>2.309</v>
+      </c>
+      <c r="F251" t="n">
+        <v>1.4665</v>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>排名下降(8→9)调出</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-06-09 10:58</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>创业板成长ETF华夏</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>sz159967</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E252" t="n">
+        <v>0.902</v>
+      </c>
+      <c r="F252" t="n">
+        <v>3.916</v>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>动量排名第1/51</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-06-11 14:48</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>创业板成长ETF华夏</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>sz159967</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E253" t="n">
+        <v>0.892</v>
+      </c>
+      <c r="F253" t="n">
+        <v>3.671</v>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>盈利保护(回撤5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-06-11 14:48</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>科创成长ETF易方达</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>sh588020</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E254" t="n">
+        <v>2.757</v>
+      </c>
+      <c r="F254" t="n">
+        <v>1.6384</v>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>动量排名第1/51</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-06-12 10:59</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>科创成长ETF易方达</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>sh588020</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E255" t="n">
+        <v>2.838</v>
+      </c>
+      <c r="F255" t="n">
+        <v>1.9656</v>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>排名下降(8→8)调出</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-06-12 10:59</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>创业板成长ETF华夏</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>sz159967</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E256" t="n">
+        <v>0.912</v>
+      </c>
+      <c r="F256" t="n">
+        <v>4.1593</v>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>动量排名第1/51</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-06-15 14:48</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>创业板成长ETF华夏</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>sz159967</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E257" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="F257" t="n">
+        <v>5.2069</v>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>排名下降(4→3)调出</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-06-15 14:48</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>中韩半导体ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>sh513310</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E258" t="n">
+        <v>5.986</v>
+      </c>
+      <c r="F258" t="n">
+        <v>14.7412</v>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>动量排名第1/51</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-06-17 14:46</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>中韩半导体ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>sh513310</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E259" t="n">
+        <v>6.197</v>
+      </c>
+      <c r="F259" t="n">
+        <v>17.0506</v>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>被过滤规则排除</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-06-17 14:46</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>创业板成长ETF华夏</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>sz159967</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E260" t="n">
+        <v>1.009</v>
+      </c>
+      <c r="F260" t="n">
+        <v>6.2801</v>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>动量排名第1/51</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-06-18 10:59</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>创业板成长ETF华夏</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>sz159967</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E261" t="n">
+        <v>1.025</v>
+      </c>
+      <c r="F261" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>排名下降(2→3)调出</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-06-18 10:59</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>中韩半导体ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>sh513310</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E262" t="n">
+        <v>6.366</v>
+      </c>
+      <c r="F262" t="n">
+        <v>18.988</v>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>动量排名第1/51</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backtest/results_qmt/七星QMT_交易记录_2026.xlsx
+++ b/backtest/results_qmt/七星QMT_交易记录_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G262"/>
+  <dimension ref="A1:G266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8580,6 +8580,138 @@
         </is>
       </c>
     </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:58</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>中韩半导体ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>sh513310</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E263" t="n">
+        <v>6.518</v>
+      </c>
+      <c r="F263" t="n">
+        <v>0.2816</v>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>排名下降(13→13)调出</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-06-25 10:58</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>科创成长ETF易方达</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>sh588020</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E264" t="n">
+        <v>3.442</v>
+      </c>
+      <c r="F264" t="n">
+        <v>7.5053</v>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>动量排名第1/50</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-07-06 10:57</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>科创成长ETF易方达</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>sh588020</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E265" t="n">
+        <v>3.203</v>
+      </c>
+      <c r="F265" t="n">
+        <v>5.6532</v>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>盈利保护(回撤6%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-07-06 10:57</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>日经ETF华夏</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>sh513520</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E266" t="n">
+        <v>2.393</v>
+      </c>
+      <c r="F266" t="n">
+        <v>2.9442</v>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>动量排名第1/50</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backtest/results_qmt/七星QMT_交易记录_2026.xlsx
+++ b/backtest/results_qmt/七星QMT_交易记录_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G266"/>
+  <dimension ref="A1:G294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8712,6 +8712,930 @@
         </is>
       </c>
     </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-07-09 10:56</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>日经ETF华夏</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>sh513520</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E267" t="n">
+        <v>2.346</v>
+      </c>
+      <c r="F267" t="n">
+        <v>2.5827</v>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>盈利保护(回撤6%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-07-09 10:56</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>科创芯片ETF嘉实</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>sh588200</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E268" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="F268" t="n">
+        <v>2.7624</v>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>动量排名第1/50</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-07-10 14:45</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>科创芯片ETF嘉实</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>sh588200</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E269" t="n">
+        <v>4.626</v>
+      </c>
+      <c r="F269" t="n">
+        <v>19.3228</v>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>盈利保护(回撤6%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-07-10 14:45</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>纳指生物科技ETF汇添富</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>sh513290</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E270" t="n">
+        <v>1.722</v>
+      </c>
+      <c r="F270" t="n">
+        <v>11.3796</v>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>动量排名第1/50</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-07-13 10:57</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>纳指生物科技ETF汇添富</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>sh513290</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E271" t="n">
+        <v>1.653</v>
+      </c>
+      <c r="F271" t="n">
+        <v>6.7666</v>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>排名下降(2→2)调出</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-07-13 10:57</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>科创芯片ETF嘉实</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>sh588200</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E272" t="n">
+        <v>4.506</v>
+      </c>
+      <c r="F272" t="n">
+        <v>8.537699999999999</v>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>动量排名第1/50</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-07-14 10:56</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>科创芯片ETF嘉实</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>sh588200</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E273" t="n">
+        <v>4.191</v>
+      </c>
+      <c r="F273" t="n">
+        <v>5.8831</v>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>盈利保护(回撤7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-07-14 10:56</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>纳指生物科技ETF汇添富</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>sh513290</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E274" t="n">
+        <v>1.601</v>
+      </c>
+      <c r="F274" t="n">
+        <v>5.6824</v>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>动量排名第1/50</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-07-17 13:07</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>纳指生物科技ETF汇添富</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>sh513290</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E275" t="n">
+        <v>1.592</v>
+      </c>
+      <c r="F275" t="n">
+        <v>0.6073</v>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>日内趋势: 换仓卖出</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-07-17 13:07</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>中概互联网ETF易方达</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>sh513050</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E276" t="n">
+        <v>1.097</v>
+      </c>
+      <c r="F276" t="n">
+        <v>0.9813</v>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>日内趋势上涨确认: 动量排名第1/50</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-07-21 14:50</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>中概互联网ETF易方达</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>sh513050</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E277" t="n">
+        <v>1.131</v>
+      </c>
+      <c r="F277" t="n">
+        <v>1.7289</v>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>排名下降(2→2)调出</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-07-21 14:50</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>南方原油LOF</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>sh501018</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E278" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="F278" t="n">
+        <v>1.8657</v>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>动量排名第1/50</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-07-22 13:06</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>南方原油LOF</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>sh501018</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E279" t="n">
+        <v>2.113</v>
+      </c>
+      <c r="F279" t="n">
+        <v>6.8137</v>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>日内趋势: 换仓卖出</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-07-22 13:06</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>豆粕ETF华夏</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>sz159985</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E280" t="n">
+        <v>2.207</v>
+      </c>
+      <c r="F280" t="n">
+        <v>1.7877</v>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>日内趋势上涨确认: 动量排名第1/50</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-07-23 13:05</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>豆粕ETF华夏</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>sz159985</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E281" t="n">
+        <v>2.257</v>
+      </c>
+      <c r="F281" t="n">
+        <v>2.0804</v>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>日内趋势: 换仓卖出</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-07-23 13:05</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>中概互联网ETF易方达</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>sh513050</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E282" t="n">
+        <v>1.098</v>
+      </c>
+      <c r="F282" t="n">
+        <v>2.3524</v>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>日内趋势上涨确认: 动量排名第1/50</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-07-24 13:05</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>中概互联网ETF易方达</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>sh513050</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E283" t="n">
+        <v>1.066</v>
+      </c>
+      <c r="F283" t="n">
+        <v>1.6087</v>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>日内趋势: 换仓卖出</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-07-24 13:05</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>南方原油LOF</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>sh501018</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E284" t="n">
+        <v>2.225</v>
+      </c>
+      <c r="F284" t="n">
+        <v>34.625</v>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>日内趋势上涨确认: 动量排名第1/50</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:05</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>南方原油LOF</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>sh501018</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E285" t="n">
+        <v>1.839</v>
+      </c>
+      <c r="F285" t="n">
+        <v>25.9404</v>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>日内趋势: 换仓卖出</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-07-28 13:05</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>港股红利ETF博时</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>sh513690</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E286" t="n">
+        <v>1.139</v>
+      </c>
+      <c r="F286" t="n">
+        <v>2.0634</v>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>日内趋势上涨确认: 动量排名第1/50</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-07-29 13:05</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>港股红利ETF博时</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>sh513690</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E287" t="n">
+        <v>1.157</v>
+      </c>
+      <c r="F287" t="n">
+        <v>2.4822</v>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>日内趋势: 换仓卖出</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-07-29 13:05</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>南方原油LOF</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>sh501018</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E288" t="n">
+        <v>1.893</v>
+      </c>
+      <c r="F288" t="n">
+        <v>19.6435</v>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>日内趋势上涨确认: 动量排名第1/50</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-07-30 14:50</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>南方原油LOF</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>sh501018</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E289" t="n">
+        <v>2.034</v>
+      </c>
+      <c r="F289" t="n">
+        <v>19.629</v>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>被过滤规则排除</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-07-30 14:50</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>港股红利ETF博时</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>sh513690</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E290" t="n">
+        <v>1.171</v>
+      </c>
+      <c r="F290" t="n">
+        <v>3.1643</v>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>动量排名第1/50</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-07-31 13:05</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>港股红利ETF博时</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>sh513690</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E291" t="n">
+        <v>1.147</v>
+      </c>
+      <c r="F291" t="n">
+        <v>2.8611</v>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>日内趋势: 换仓卖出</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-07-31 13:05</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>南方原油LOF</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>sh501018</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E292" t="n">
+        <v>1.977</v>
+      </c>
+      <c r="F292" t="n">
+        <v>14.0659</v>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>日内趋势上涨确认: 动量排名第1/50</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-08-06 13:05</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>南方原油LOF</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>sh501018</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E293" t="n">
+        <v>1.974</v>
+      </c>
+      <c r="F293" t="n">
+        <v>1.9635</v>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>日内趋势: 换仓卖出</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-08-06 13:05</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>中概互联网ETF易方达</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>sh513050</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E294" t="n">
+        <v>1.163</v>
+      </c>
+      <c r="F294" t="n">
+        <v>1.4577</v>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>日内趋势上涨确认: 动量排名第1/50</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/backtest/results_qmt/七星QMT_交易记录_2026.xlsx
+++ b/backtest/results_qmt/七星QMT_交易记录_2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G294"/>
+  <dimension ref="A1:G310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9636,6 +9636,534 @@
         </is>
       </c>
     </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-08-10 13:05</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>中概互联网ETF易方达</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>sh513050</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E295" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="F295" t="n">
+        <v>0.9266</v>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>日内趋势: 换仓卖出</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-08-10 13:05</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>有色金属ETF南方</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>sh512400</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E296" t="n">
+        <v>1.986</v>
+      </c>
+      <c r="F296" t="n">
+        <v>2.125</v>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>日内趋势上涨确认: 动量排名第1/50</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-08-13 14:50</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>有色金属ETF南方</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>sh512400</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E297" t="n">
+        <v>1.869</v>
+      </c>
+      <c r="F297" t="n">
+        <v>2.5042</v>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>盈利保护(回撤5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-08-13 14:50</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>标普500ETF博时</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>sh513500</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E298" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="F298" t="n">
+        <v>0.8794</v>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>动量排名第1/50</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-08-14 13:05</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>标普500ETF博时</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>sh513500</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E299" t="n">
+        <v>2.749</v>
+      </c>
+      <c r="F299" t="n">
+        <v>1.154</v>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>日内趋势: 换仓卖出</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-08-14 13:05</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>有色金属ETF南方</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>sh512400</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E300" t="n">
+        <v>1.873</v>
+      </c>
+      <c r="F300" t="n">
+        <v>2.3558</v>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>日内趋势上涨确认: 动量排名第1/50</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-08-21 13:05</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>有色金属ETF南方</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>sh512400</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E301" t="n">
+        <v>1.929</v>
+      </c>
+      <c r="F301" t="n">
+        <v>1.6272</v>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>日内趋势: 换仓卖出</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-08-21 13:05</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>中证2000ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>sh563300</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E302" t="n">
+        <v>1.401</v>
+      </c>
+      <c r="F302" t="n">
+        <v>2.2406</v>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>日内趋势上涨确认: 动量排名第1/50</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-08-24 13:05</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>中证2000ETF华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>sh563300</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E303" t="n">
+        <v>1.379</v>
+      </c>
+      <c r="F303" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>日内趋势: 换仓卖出</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-08-24 13:05</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>纳指生物科技ETF汇添富</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>sh513290</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E304" t="n">
+        <v>1.836</v>
+      </c>
+      <c r="F304" t="n">
+        <v>3.0212</v>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>日内趋势上涨确认: 动量排名第1/50</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-08-27 13:05</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>纳指生物科技ETF汇添富</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>sh513290</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E305" t="n">
+        <v>1.831</v>
+      </c>
+      <c r="F305" t="n">
+        <v>4.5968</v>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>日内趋势: 换仓卖出</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-08-27 13:05</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>黄金ETF华安</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>sh518880</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E306" t="n">
+        <v>9.492000000000001</v>
+      </c>
+      <c r="F306" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>日内趋势上涨确认: 动量排名第1/50</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-08-28 13:05</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>黄金ETF华安</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>sh518880</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E307" t="n">
+        <v>9.413</v>
+      </c>
+      <c r="F307" t="n">
+        <v>2.8911</v>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>日内趋势: 换仓卖出</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-08-28 13:05</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>纳指生物科技ETF汇添富</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>sh513290</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E308" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="F308" t="n">
+        <v>4.778</v>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>日内趋势上涨确认: 动量排名第1/50</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-09-02 14:55</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>纳指生物科技ETF汇添富</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>sh513290</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>卖出</t>
+        </is>
+      </c>
+      <c r="E309" t="n">
+        <v>1.791</v>
+      </c>
+      <c r="F309" t="n">
+        <v>2.4245</v>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>排名下降(1→2)调出</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-09-02 14:55</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>豆粕ETF华夏</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>sz159985</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
+      <c r="E310" t="n">
+        <v>2.346</v>
+      </c>
+      <c r="F310" t="n">
+        <v>2.4464</v>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>动量排名第1/50</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
